--- a/electricity2025.xlsx
+++ b/electricity2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Downloads OS\Data Engineering\tutorialz\timeSeries\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6CA42D3-D5CE-4AFB-8D6F-B998FE68D2AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{599B1443-B369-49F3-9486-D6E704EF2E28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F4733A1C-19F0-4E7D-AFDE-2FA5E5D9482A}"/>
+    <workbookView xWindow="1428" yWindow="1428" windowWidth="17280" windowHeight="8880" xr2:uid="{F4733A1C-19F0-4E7D-AFDE-2FA5E5D9482A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,40 +41,40 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
-    <t>January</t>
+    <t>2025-01</t>
   </si>
   <si>
-    <t>February</t>
+    <t>2025-02</t>
   </si>
   <si>
-    <t>March</t>
+    <t>2025-03</t>
   </si>
   <si>
-    <t>April</t>
+    <t>2025-04</t>
   </si>
   <si>
-    <t>May</t>
+    <t>2025-05</t>
   </si>
   <si>
-    <t>June</t>
+    <t>2025-06</t>
   </si>
   <si>
-    <t>July</t>
+    <t>2025-07</t>
   </si>
   <si>
-    <t>August</t>
+    <t>2025-08</t>
   </si>
   <si>
-    <t>Sept</t>
+    <t>2025-09</t>
   </si>
   <si>
-    <t>October</t>
+    <t>2025-10</t>
   </si>
   <si>
-    <t>November</t>
+    <t>2025-11</t>
   </si>
   <si>
-    <t>December</t>
+    <t>2025-12</t>
   </si>
 </sst>
 </file>
@@ -1164,7 +1164,7 @@
         <v>320588</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>299022</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
